--- a/SQL/PostgreSQL/Projeto Vendas/Dados/base_vendedores.xlsx
+++ b/SQL/PostgreSQL/Projeto Vendas/Dados/base_vendedores.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>id_vendedor</t>
   </si>
@@ -59,6 +59,45 @@
   </si>
   <si>
     <t>Iyo Sky</t>
+  </si>
+  <si>
+    <t>Funny Valentine</t>
+  </si>
+  <si>
+    <t>Vinsmoke Sanji</t>
+  </si>
+  <si>
+    <t>Frank Castle</t>
+  </si>
+  <si>
+    <t>Albert Simmons</t>
+  </si>
+  <si>
+    <t>Udyr Spiritwalker</t>
+  </si>
+  <si>
+    <t>Bi-Han</t>
+  </si>
+  <si>
+    <t>Jardani Jovanovich</t>
+  </si>
+  <si>
+    <t>Michael Scofield</t>
+  </si>
+  <si>
+    <t>Roman Reigns</t>
+  </si>
+  <si>
+    <t>Cody Rhodes</t>
+  </si>
+  <si>
+    <t>Trick Williams</t>
+  </si>
+  <si>
+    <t>Geralt de Rívia</t>
+  </si>
+  <si>
+    <t>Oba Femi</t>
   </si>
 </sst>
 </file>
@@ -904,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="2" customWidth="1"/>
@@ -971,7 +1010,112 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>